--- a/Config/Datas/yc_attribute.xlsx
+++ b/Config/Datas/yc_attribute.xlsx
@@ -1077,7 +1077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="57.625" customWidth="1" style="1" min="11" max="11"/>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="K16" s="0" t="inlineStr">
         <is>
-          <t>固定堕落增加</t>
+          <t>遗留：固定堕落增加（日结已改用FallenBase*）</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
     <row r="28">
       <c r="H28" s="0" t="inlineStr">
         <is>
-          <t>PartGearPoint_Womb</t>
+          <t>PartGearPoint_FrontHole</t>
         </is>
       </c>
       <c r="J28" s="0" t="n">
@@ -1594,14 +1594,14 @@
       </c>
       <c r="K28" s="0" t="inlineStr">
         <is>
-          <t>子宫装备点</t>
+          <t>前穴装备点</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t>PartGearPoint_Tail</t>
+          <t>PartGearPoint_BackHole</t>
         </is>
       </c>
       <c r="J29" s="0" t="n">
@@ -1609,39 +1609,19 @@
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t>尾部装备点</t>
+          <t>后穴装备点</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="H30" s="0" t="inlineStr">
-        <is>
-          <t>PartGearPoint_Wing</t>
-        </is>
-      </c>
-      <c r="J30" s="0" t="n">
-        <v>104</v>
-      </c>
-      <c r="K30" s="0" t="inlineStr">
-        <is>
-          <t>翅膀装备点</t>
-        </is>
-      </c>
+      <c r="H30" s="0" t="n"/>
+      <c r="J30" s="0" t="n"/>
+      <c r="K30" s="0" t="n"/>
     </row>
     <row r="31">
-      <c r="H31" s="0" t="inlineStr">
-        <is>
-          <t>PartGearPoint_Skin</t>
-        </is>
-      </c>
-      <c r="J31" s="0" t="n">
-        <v>105</v>
-      </c>
-      <c r="K31" s="0" t="inlineStr">
-        <is>
-          <t>皮肤装备点</t>
-        </is>
-      </c>
+      <c r="H31" s="0" t="n"/>
+      <c r="J31" s="0" t="n"/>
+      <c r="K31" s="0" t="n"/>
     </row>
     <row r="32"/>
     <row r="33">
@@ -1882,6 +1862,111 @@
       <c r="K49" s="0" t="inlineStr">
         <is>
           <t>H强度</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="H50" s="0" t="inlineStr">
+        <is>
+          <t>InnerArmMinExposeRate</t>
+        </is>
+      </c>
+      <c r="J50" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="K50" s="0" t="inlineStr">
+        <is>
+          <t>Part Gear / exposed armor tuning</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="H51" s="0" t="inlineStr">
+        <is>
+          <t>HPMax</t>
+        </is>
+      </c>
+      <c r="J51" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="K51" s="0" t="inlineStr">
+        <is>
+          <t>通用生命上限养成属性</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="H52" s="0" t="inlineStr">
+        <is>
+          <t>FallenBaseDailyAdd</t>
+        </is>
+      </c>
+      <c r="J52" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="K52" s="0" t="inlineStr">
+        <is>
+          <t>每日基础沉沦增长（默认0，需天赋等开启）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>FallenBaseDailyHomeProsperityNeed</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>41</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>基础沉沦家繁荣门槛；&gt;0且达标才加FromHome日增</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>FallenBaseDailyAddFromHome</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>42</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>家繁荣达标时每日额外基础沉沦</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>FallenSpreadCapMul</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>43</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>扩散人数上限倍数：上限=基础*该值（默认10）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>FallenSpreadGrowthPermille</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>44</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>扩散日增千分比系数（默认100=0.1）</t>
         </is>
       </c>
     </row>
